--- a/controlCommand.xlsx
+++ b/controlCommand.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nimis\Documents\MATLAB\CUonOrbit\ADCS_sim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE904CDA-3359-4EBA-BFC1-C7D38EEE41C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21F06FF5-C01B-4719-B048-9E507185F70C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="2775" windowWidth="20430" windowHeight="11400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="13770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="commands" sheetId="2" r:id="rId1"/>
@@ -400,17 +400,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{694C082E-BA2A-44C1-A93A-2F9CB2B05B5C}">
-  <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E22"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.28515625" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.26953125" customWidth="1"/>
+    <col min="3" max="3" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -427,9 +427,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
-        <v>45658.666666666664</v>
+        <v>45829</v>
       </c>
       <c r="B2">
         <f>(A2 - A$2) * 86400</f>
@@ -445,10 +445,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <f>A2 + TIME(0, 30, 0)</f>
-        <v>45658.6875</v>
+        <v>45829.020833333336</v>
       </c>
       <c r="B3">
         <f>(A3 - A$2) * 86400</f>
@@ -464,17 +464,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
-        <f>A2 + TIME(0, 0, 2 * 5701.76)</f>
-        <v>45658.798645833333</v>
+        <v>45829.133333333331</v>
       </c>
       <c r="B4">
-        <f t="shared" ref="B4:B9" si="0">(A4 - A$2) * 86400</f>
-        <v>11403.000000142492</v>
+        <f t="shared" ref="B4:B21" si="0">(A4 - A$2) * 86400</f>
+        <v>11519.999999832362</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -483,37 +482,35 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
-        <f>A4 + TIME(0, 25, 0)</f>
-        <v>45658.816006944442</v>
+        <v>45829.146909722222</v>
       </c>
       <c r="B5">
         <f t="shared" si="0"/>
-        <v>12903.000000002794</v>
+        <v>12692.999999946915</v>
       </c>
       <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="1">
+        <v>45829.46875</v>
+      </c>
+      <c r="B6">
+        <f t="shared" si="0"/>
+        <v>40500</v>
+      </c>
+      <c r="C6">
         <v>3</v>
       </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <f>A5 + TIME(0, 15, 0)</f>
-        <v>45658.826423611106</v>
-      </c>
-      <c r="B6">
-        <f t="shared" si="0"/>
-        <v>13802.999999793246</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
       <c r="D6">
         <v>0</v>
       </c>
@@ -521,14 +518,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
-        <f>A4 + TIME(0, 0, 5701.76)</f>
-        <v>45658.864629629628</v>
+        <v>45829.480104166665</v>
       </c>
       <c r="B7">
         <f t="shared" si="0"/>
-        <v>17104.000000096858</v>
+        <v>41480.99999986589</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -540,17 +536,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
-        <f>A7 + TIME(0, 0, 5701.76/2)</f>
-        <v>45658.897615740738</v>
+        <v>45829.534722222219</v>
       </c>
       <c r="B8">
         <f t="shared" si="0"/>
-        <v>19953.999999957159</v>
+        <v>46199.999999720603</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -559,14 +554,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
-        <f t="shared" ref="A9" si="1">A8 + TIME(0, 0, 5701.76)</f>
-        <v>45658.963599537034</v>
+        <v>45829.547650462962</v>
       </c>
       <c r="B9">
         <f t="shared" si="0"/>
-        <v>25654.999999911524</v>
+        <v>47316.999999945983</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -578,8 +572,224 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" s="1">
+        <v>45829.607638888891</v>
+      </c>
+      <c r="B10">
+        <f t="shared" si="0"/>
+        <v>52500.000000139698</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" s="1">
+        <v>45829.622997685183</v>
+      </c>
+      <c r="B11">
+        <f t="shared" si="0"/>
+        <v>53826.999999792315</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" s="1">
+        <v>45829.673611111109</v>
+      </c>
+      <c r="B12">
+        <f t="shared" si="0"/>
+        <v>58199.999999860302</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" s="1">
+        <v>45829.687951388885</v>
+      </c>
+      <c r="B13">
+        <f t="shared" si="0"/>
+        <v>59438.999999687076</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" s="1">
+        <v>45829.739583333336</v>
+      </c>
+      <c r="B14">
+        <f t="shared" si="0"/>
+        <v>63900.000000209548</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" s="1">
+        <v>45829.754143518519</v>
+      </c>
+      <c r="B15">
+        <f t="shared" si="0"/>
+        <v>65158.0000000773</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" s="1">
+        <v>45829.805555555555</v>
+      </c>
+      <c r="B16">
+        <f t="shared" si="0"/>
+        <v>69599.999999930151</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" s="1">
+        <v>45829.818287037036</v>
+      </c>
+      <c r="B17">
+        <f t="shared" si="0"/>
+        <v>70699.999999953434</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" s="1">
+        <v>45829.916666666664</v>
+      </c>
+      <c r="B18">
+        <f t="shared" si="0"/>
+        <v>79199.999999790452</v>
+      </c>
+      <c r="C18">
+        <v>3</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" s="1">
+        <v>45829.929548611108</v>
+      </c>
+      <c r="B19">
+        <f t="shared" si="0"/>
+        <v>80312.999999709427</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" s="1">
+        <v>45829.94027777778</v>
+      </c>
+      <c r="B20">
+        <f t="shared" si="0"/>
+        <v>81240.000000153668</v>
+      </c>
+      <c r="C20">
+        <v>3</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" s="1">
+        <v>45829.995740740742</v>
+      </c>
+      <c r="B21">
+        <f t="shared" si="0"/>
+        <v>86032.000000099652</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -589,15 +799,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.26953125" customWidth="1"/>
+    <col min="3" max="3" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -605,7 +815,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>0</v>
       </c>
@@ -613,7 +823,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
@@ -621,7 +831,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -629,7 +839,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -637,7 +847,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -645,7 +855,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -653,7 +863,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
